--- a/survey_templates/042_online_shopping_survey--survey_templates.xlsx
+++ b/survey_templates/042_online_shopping_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>somewhat_good</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>somewhat_good</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>very_fast</t>
+          <t>very fast</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>somewhat_fast</t>
+          <t>somewhat fast</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>very_slow</t>
+          <t>very slow</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>very_strict</t>
+          <t>very strict</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>somewhat_strict</t>
+          <t>somewhat strict</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>very_relaxed</t>
+          <t>very relaxed</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>somewhat_good</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>very_relevant</t>
+          <t>very relevant</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>somewhat_relevant</t>
+          <t>somewhat relevant</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>very_irrelevant</t>
+          <t>very irrelevant</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>very_easy</t>
+          <t>very easy</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>somewhat_easy</t>
+          <t>somewhat easy</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>very_difficult</t>
+          <t>very difficult</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>very_friendly</t>
+          <t>very friendly</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>somewhat_friendly</t>
+          <t>somewhat friendly</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>very_unfriendly</t>
+          <t>very unfriendly</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>somewhat_good</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>very_intuitive</t>
+          <t>very intuitive</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>somewhat_intuitive</t>
+          <t>somewhat intuitive</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>very_non_intuitive</t>
+          <t>very non intuitive</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>somewhat_good</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>very_easy</t>
+          <t>very easy</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>somewhat_easy</t>
+          <t>somewhat easy</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>very_difficult</t>
+          <t>very difficult</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>very_affordable</t>
+          <t>very affordable</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>somewhat_affordable</t>
+          <t>somewhat affordable</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>very_expensive</t>
+          <t>very expensive</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>always_available</t>
+          <t>always available</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sometimes_available</t>
+          <t>sometimes available</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>never_available</t>
+          <t>never available</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>very_friendly</t>
+          <t>very friendly</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>somewhat_friendly</t>
+          <t>somewhat friendly</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>very_unfriendly</t>
+          <t>very unfriendly</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>always_return</t>
+          <t>always return</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sometimes_return</t>
+          <t>sometimes return</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>never_return</t>
+          <t>never return</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>somewhat_good</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>always_warranty</t>
+          <t>always warranty</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sometimes_warranty</t>
+          <t>sometimes warranty</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>never_warranty</t>
+          <t>never warranty</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>very_fast</t>
+          <t>very fast</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>somewhat_fast</t>
+          <t>somewhat fast</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>very_slow</t>
+          <t>very slow</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>very_strict</t>
+          <t>very strict</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>somewhat_strict</t>
+          <t>somewhat strict</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>very_relaxed</t>
+          <t>very relaxed</t>
         </is>
       </c>
     </row>
